--- a/assets/template-pembukuan-umkm.xlsx
+++ b/assets/template-pembukuan-umkm.xlsx
@@ -569,7 +569,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>PPh Final 0,5% mengikuti PP 55/2022: orang pribadi tidak dikenai pajak atas omzet sampai Rp500 juta setahun.</t>
+          <t>PPh Final 0,5% mengikuti PP 55/2022 sebagaimana diubah PP 20/2026: orang pribadi tidak dikenai pajak atas omzet sampai Rp500 juta setahun.</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PP 55/2022: Rp500 juta hanya untuk orang pribadi, badan Rp0.</t>
+          <t>Rp500 juta hanya untuk orang pribadi; PT perorangan dan koperasi Rp0.</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PP 55/2022 Pasal 57. Cek perubahan aturan di pajak.go.id.</t>
+          <t>PP 55/2022 jo. PP 20/2026. Cek perubahan aturan di pajak.go.id.</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"Orang pribadi,Badan"</formula1>
+      <formula1>"Orang pribadi,PT perorangan/koperasi"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/template-pembukuan-umkm.xlsx
+++ b/assets/template-pembukuan-umkm.xlsx
@@ -583,7 +583,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Kalkulator dan panduan lainnya: https://labakita.pages.dev</t>
+          <t>Kalkulator dan panduan lainnya: https://labakita.wjzyy9fpzd.workers.dev</t>
         </is>
       </c>
     </row>
